--- a/Data/Procesados/Resultados_Congruencia_Por_Categoria.xlsx
+++ b/Data/Procesados/Resultados_Congruencia_Por_Categoria.xlsx
@@ -500,13 +500,13 @@
         <v>425</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8541176470588235</v>
+        <v>0.1220168067226891</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.7529411764705882</v>
+        <v>-0.107563025210084</v>
       </c>
       <c r="H2" t="n">
-        <v>7.347542033760345e-08</v>
+        <v>1.297604890878342e-07</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -539,13 +539,13 @@
         <v>425</v>
       </c>
       <c r="F3" t="n">
-        <v>-16.00421411764706</v>
+        <v>-2.286316302521008</v>
       </c>
       <c r="G3" t="n">
-        <v>-14.7747305882353</v>
+        <v>-2.110675798319328</v>
       </c>
       <c r="H3" t="n">
-        <v>4.971929482403652e-07</v>
+        <v>4.966819799945477e-07</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -578,13 +578,13 @@
         <v>1257</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9665871121718377</v>
+        <v>0.1380838731674054</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.7764518695306285</v>
+        <v>-0.1109216956472327</v>
       </c>
       <c r="H4" t="n">
-        <v>5.872499166598002e-24</v>
+        <v>5.467351153262559e-24</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -617,13 +617,13 @@
         <v>1257</v>
       </c>
       <c r="F5" t="n">
-        <v>-19.41125338106603</v>
+        <v>-2.773036197295147</v>
       </c>
       <c r="G5" t="n">
-        <v>-17.91983770883055</v>
+        <v>-2.559976815547222</v>
       </c>
       <c r="H5" t="n">
-        <v>2.247490839497724e-10</v>
+        <v>2.245224331178344e-10</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -656,13 +656,13 @@
         <v>84</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1726190476190476</v>
+        <v>0.02465986394557824</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.4940476190476191</v>
+        <v>-0.07057823129251702</v>
       </c>
       <c r="H6" t="n">
-        <v>0.667781101001432</v>
+        <v>0.5800163539712654</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -695,10 +695,10 @@
         <v>84</v>
       </c>
       <c r="F7" t="n">
-        <v>-20.68978571428572</v>
+        <v>-2.955683673469388</v>
       </c>
       <c r="G7" t="n">
-        <v>-19.1716369047619</v>
+        <v>-2.738805272108843</v>
       </c>
       <c r="H7" t="n">
         <v>0.3134978401660627</v>
@@ -734,13 +734,13 @@
         <v>208</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7259615384615384</v>
+        <v>0.1037087912087912</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.3894230769230769</v>
+        <v>-0.05563186813186813</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01738265019930525</v>
+        <v>0.0198093761717871</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -773,10 +773,10 @@
         <v>208</v>
       </c>
       <c r="F9" t="n">
-        <v>-22.26426201923077</v>
+        <v>-3.18060885989011</v>
       </c>
       <c r="G9" t="n">
-        <v>-21.70120673076923</v>
+        <v>-3.10017239010989</v>
       </c>
       <c r="H9" t="n">
         <v>0.7239077408302327</v>
@@ -812,13 +812,13 @@
         <v>212</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8066037735849056</v>
+        <v>0.1152291105121294</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.2924528301886792</v>
+        <v>-0.04177897574123988</v>
       </c>
       <c r="H10" t="n">
-        <v>0.01021221424803583</v>
+        <v>0.01104447760424978</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -851,10 +851,10 @@
         <v>212</v>
       </c>
       <c r="F11" t="n">
-        <v>-18.76673820754717</v>
+        <v>-2.680962601078167</v>
       </c>
       <c r="G11" t="n">
-        <v>-19.61653301886793</v>
+        <v>-2.802361859838275</v>
       </c>
       <c r="H11" t="n">
         <v>0.09280450228905059</v>
@@ -890,13 +890,13 @@
         <v>185</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5567567567567567</v>
+        <v>0.07953667953667955</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.6162162162162163</v>
+        <v>-0.08803088803088803</v>
       </c>
       <c r="H12" t="n">
-        <v>0.002279928561499132</v>
+        <v>0.002047559219123162</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -929,10 +929,10 @@
         <v>185</v>
       </c>
       <c r="F13" t="n">
-        <v>-25.79164864864865</v>
+        <v>-3.684521235521235</v>
       </c>
       <c r="G13" t="n">
-        <v>-22.16985675675676</v>
+        <v>-3.167122393822394</v>
       </c>
       <c r="H13" t="n">
         <v>0.004163811955591786</v>
@@ -968,13 +968,13 @@
         <v>133</v>
       </c>
       <c r="F14" t="n">
-        <v>0.02255639097744361</v>
+        <v>0.003222341568206242</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.5789473684210527</v>
+        <v>-0.08270676691729321</v>
       </c>
       <c r="H14" t="n">
-        <v>0.877352108907123</v>
+        <v>0.8601811162841806</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1007,13 +1007,13 @@
         <v>133</v>
       </c>
       <c r="F15" t="n">
-        <v>-16.97471804511278</v>
+        <v>-2.424959720730397</v>
       </c>
       <c r="G15" t="n">
-        <v>-17.65567293233083</v>
+        <v>-2.522238990332975</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5585263121316696</v>
+        <v>0.5592814597964171</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1046,13 +1046,13 @@
         <v>597</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5125628140703518</v>
+        <v>0.07322325915290738</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.169179229480737</v>
+        <v>-0.024168461354391</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0094612312000834</v>
+        <v>0.009120642834786828</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1085,13 +1085,13 @@
         <v>597</v>
       </c>
       <c r="F17" t="n">
-        <v>-16.56001256281407</v>
+        <v>-2.36571608040201</v>
       </c>
       <c r="G17" t="n">
-        <v>-15.61237604690117</v>
+        <v>-2.230339435271596</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0008295518578608235</v>
+        <v>0.0008295518929929839</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1124,13 +1124,13 @@
         <v>43</v>
       </c>
       <c r="F18" t="n">
-        <v>1.325581395348837</v>
+        <v>0.1893687707641196</v>
       </c>
       <c r="G18" t="n">
-        <v>0.4534883720930232</v>
+        <v>0.06478405315614616</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1631229948688568</v>
+        <v>0.1698948384834541</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1163,10 +1163,10 @@
         <v>43</v>
       </c>
       <c r="F19" t="n">
-        <v>-21.81169767441861</v>
+        <v>-3.115956810631229</v>
       </c>
       <c r="G19" t="n">
-        <v>-25.18326744186047</v>
+        <v>-3.597609634551495</v>
       </c>
       <c r="H19" t="n">
         <v>0.5298736895283582</v>
@@ -1202,13 +1202,13 @@
         <v>45</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.01904761904761904</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.3555555555555556</v>
+        <v>-0.0507936507936508</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3113185348688483</v>
+        <v>0.3072510082946803</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1241,10 +1241,10 @@
         <v>45</v>
       </c>
       <c r="F21" t="n">
-        <v>-22.52531111111111</v>
+        <v>-3.217901587301587</v>
       </c>
       <c r="G21" t="n">
-        <v>-17.75966666666667</v>
+        <v>-2.537095238095238</v>
       </c>
       <c r="H21" t="n">
         <v>0.1563360387753505</v>
@@ -1280,13 +1280,13 @@
         <v>116</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3189655172413793</v>
+        <v>0.04556650246305417</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.418103448275862</v>
+        <v>-0.05972906403940887</v>
       </c>
       <c r="H22" t="n">
-        <v>0.4638870319227534</v>
+        <v>0.4753564188791719</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1319,10 +1319,10 @@
         <v>116</v>
       </c>
       <c r="F23" t="n">
-        <v>-16.75397844827586</v>
+        <v>-2.393425492610838</v>
       </c>
       <c r="G23" t="n">
-        <v>-12.8175474137931</v>
+        <v>-1.831078201970444</v>
       </c>
       <c r="H23" t="n">
         <v>0.03389887794583088</v>
@@ -1358,13 +1358,13 @@
         <v>93</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.08602150537634409</v>
+        <v>-0.01228878648233487</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.5698924731182796</v>
+        <v>-0.08141321044546851</v>
       </c>
       <c r="H24" t="n">
-        <v>0.9943682088579749</v>
+        <v>0.9690568332542225</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1397,10 +1397,10 @@
         <v>93</v>
       </c>
       <c r="F25" t="n">
-        <v>-19.38156451612903</v>
+        <v>-2.768794930875577</v>
       </c>
       <c r="G25" t="n">
-        <v>-14.67310215053764</v>
+        <v>-2.096157450076805</v>
       </c>
       <c r="H25" t="n">
         <v>0.1267883741044678</v>
